--- a/out/Attention_Base_repeat_1_000007.xlsx
+++ b/out/Attention_Base_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>10.67907012395075</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>11.27907012395075</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.1214785345699065</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.1214785345699065</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.350885619758629e-05</v>
+        <v>-5.1119644884835e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.7321632397323752</v>
+        <v>0.5893340066480393</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.46545842325624</v>
+        <v>1.179579017313987</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1097911438137972</v>
+        <v>0.08837326318364065</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9518947012812844</v>
+        <v>0.7662005697334192</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1372747102358227</v>
+        <v>0.1104952770391442</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.116670368164936</v>
+        <v>0.8988320084949735</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1967826461112384</v>
+        <v>0.158394618297549</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.373038420346467</v>
+        <v>1.105188212009103</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2105184526747808</v>
+        <v>0.1694508668064311</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.597307351345162</v>
+        <v>1.285707136942438</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2231063901292494</v>
+        <v>0.1795837644107526</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.833019085469454</v>
+        <v>1.475436621302852</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1006837643598522</v>
+        <v>0.08104214697792185</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.811094679552205</v>
+        <v>1.45778925018872</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04862565627917254</v>
+        <v>0.03914029599657854</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.807583232453053</v>
+        <v>1.454962814317222</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02316867753908389</v>
+        <v>0.01864918576157993</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.805256255114777</v>
+        <v>1.453089807022435</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006862180623952113</v>
+        <v>0.005522313829901992</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.795788932819602</v>
+        <v>1.445468693838708</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004536897260261469</v>
+        <v>0.003650626514449602</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.797998640916994</v>
+        <v>1.447246286746994</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002320085942499</v>
+        <v>0.001866482633361447</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.798098252506395</v>
+        <v>1.447325489558267</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00118386798434055</v>
+        <v>0.0009523356927246939</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.79814552668101</v>
+        <v>1.44736256501952</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004423189860551449</v>
+        <v>0.0003545203356619184</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.79784438854966</v>
+        <v>1.44711930206168</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002383767632912877</v>
+        <v>0.0001913514225875474</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.797879399410737</v>
+        <v>1.447146526985901</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001126200326826326</v>
+        <v>8.95728641164411e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.797865283292404</v>
+        <v>1.447134197133999</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.781267869019299e-05</v>
+        <v>5.305335192866738e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.797888233616753</v>
+        <v>1.44715167130457</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.308665882696171e-05</v>
+        <v>2.588107472456355e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.797886551950965</v>
+        <v>1.447149361845824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>9.986396961777667e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.797880408501921</v>
+        <v>1.447143434231955</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>3.954024644338981e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.797880721933198</v>
+        <v>1.447142629209551</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.280563881834207e-07</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.797874578137222</v>
+        <v>1.44713671417277</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.797868893603194</v>
+        <v>1.447131166044549</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.79786414232798</v>
+        <v>1.447126331410231</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.797858853180418</v>
+        <v>1.447126187426323</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.797858830446117</v>
+        <v>1.447126164692022</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.797859148726333</v>
+        <v>1.447126482972238</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.797860239972791</v>
+        <v>1.447127574218696</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.797859550365655</v>
+        <v>1.447126884611559</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.797859580678056</v>
+        <v>1.447126914923961</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.797859391225546</v>
+        <v>1.447126725471451</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4785214654300935</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.797859444272249</v>
+        <v>1.447126778518154</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4785214654300935</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.797859497318952</v>
+        <v>1.447126831564857</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4785214654300935</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.79785945942845</v>
+        <v>1.447126793674354</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4785214654300935</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.797859330600743</v>
+        <v>1.447126664846648</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4785214654300935</v>
+        <v>6.048042895279977</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.797859186616836</v>
+        <v>1.44712652086274</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.04098559548271052</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.797859027476727</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.79785908052343</v>
+        <v>1.447126414769335</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4785214654300935</v>
+        <v>5.448042895279977</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.797859027476727</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.797859027476727</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.797858845602318</v>
+        <v>1.447126179848222</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.797859012320526</v>
+        <v>1.447126346566431</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.797859209351137</v>
+        <v>1.447126543597042</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4785214654300935</v>
+        <v>5.448042895279977</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.797859050211029</v>
+        <v>1.447126384456934</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.04098559548271052</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.79785908810153</v>
+        <v>1.447126422347435</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.04098559548271052</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.797859285132141</v>
+        <v>1.447126619378046</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.79785926239784</v>
+        <v>1.447126596643745</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.797859110835832</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.797859035054828</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.797859133570133</v>
+        <v>1.447126467816038</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.797859141148233</v>
+        <v>1.447126475394138</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.797859406381747</v>
+        <v>1.447126740627652</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.797859110835832</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.797859353335044</v>
+        <v>1.447126687580949</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.797859436694148</v>
+        <v>1.447126770940053</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.79785926997594</v>
+        <v>1.447126604221844</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.79785945942845</v>
+        <v>1.447126793674354</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.797859110835832</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.797858906227121</v>
+        <v>1.447126240473026</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.797859019898627</v>
+        <v>1.447126354144532</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.797859035054828</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.797858800133715</v>
+        <v>1.44712613437962</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.797858860758518</v>
+        <v>1.447126195004423</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.797858731930812</v>
+        <v>1.447126066176717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.797858868336619</v>
+        <v>1.447126202582524</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.797859042632928</v>
+        <v>1.447126376878833</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.797859186616836</v>
+        <v>1.44712652086274</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.797859019898627</v>
+        <v>1.447126354144532</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.797859012320526</v>
+        <v>1.447126346566431</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.797858724352711</v>
+        <v>1.447126058598616</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.797858739508913</v>
+        <v>1.447126073754817</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.797858966851924</v>
+        <v>1.447126301097829</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.797858951695724</v>
+        <v>1.447126285941628</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.797859057789129</v>
+        <v>1.447126392035033</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.797858784977515</v>
+        <v>1.447126119223419</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.79785888349282</v>
+        <v>1.447126217738725</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.797859035054828</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.797859050211029</v>
+        <v>1.447126384456934</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.797859027476727</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.797859110835832</v>
+        <v>1.447126445081736</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.797859209351137</v>
+        <v>1.447126543597042</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.797859042632928</v>
+        <v>1.447126376878833</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.797859027476727</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.797858997164326</v>
+        <v>1.447126331410231</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.797858982008125</v>
+        <v>1.44712631625403</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.797859019898627</v>
+        <v>1.447126354144532</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.797859035054828</v>
+        <v>1.447126369300732</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.6409855954827105</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.797859027476727</v>
+        <v>1.447126361722632</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_1_000007.xlsx
+++ b/out/Attention_Base_repeat_1_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4785214654300935</v>
+        <v>1.338792640423968</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>10.67907012395075</v>
+        <v>1.839195093615979</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>11.27907012395075</v>
+        <v>2.039195093615978</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.1214785345699065</v>
+        <v>1.038390187231957</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.1214785345699065</v>
+        <v>0.0375852808479359</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4785214654300935</v>
+        <v>0.0375852808479359</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.350885619758629e-05</v>
+        <v>-8.76145628024824e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.7321632397323752</v>
+        <v>1.010066510700142</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.46545842325624</v>
+        <v>2.02169440194039</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1097911438137972</v>
+        <v>0.1514639789595488</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9518947012812844</v>
+        <v>1.313200200967344</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1372747102358227</v>
+        <v>0.1893792001503588</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.116670368164936</v>
+        <v>1.540518789421072</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1967826461112384</v>
+        <v>0.2714741853033066</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.373038420346467</v>
+        <v>1.89419504712886</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2105184526747808</v>
+        <v>0.2904239527861504</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.597307351345162</v>
+        <v>2.203588682699544</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2231063901292494</v>
+        <v>0.3077908522944665</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.833019085469454</v>
+        <v>2.528768410879833</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1006837643598522</v>
+        <v>0.1389002871077845</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.811094679552205</v>
+        <v>2.498522359825531</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04862565627917254</v>
+        <v>0.06708184685886588</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.807583232453053</v>
+        <v>2.493678136931575</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02316867753908389</v>
+        <v>0.0319625028745364</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.805256255114777</v>
+        <v>2.490467962910455</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006862180623952113</v>
+        <v>0.009468526714113601</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.795788932819602</v>
+        <v>2.477409343390351</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004536897260261469</v>
+        <v>0.006261376347014713</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.797998640916994</v>
+        <v>2.480459613366261</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002320085942499</v>
+        <v>0.003201709727720796</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.798098252506395</v>
+        <v>2.480598914208837</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00118386798434055</v>
+        <v>0.001635859284060201</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.79814552668101</v>
+        <v>2.480666030930016</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004423189860551449</v>
+        <v>0.0006118612075041338</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.79784438854966</v>
+        <v>2.480252650935008</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002383767632912877</v>
+        <v>0.0003307774327442512</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.797879399410737</v>
+        <v>2.480302826466306</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001126200326826326</v>
+        <v>0.000157124909913899</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.797865283292404</v>
+        <v>2.480285261005901</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.781267869019299e-05</v>
+        <v>9.536342197837412e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.797888233616753</v>
+        <v>2.480318787128652</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.308665882696171e-05</v>
+        <v>4.749782703175804e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.797886551950965</v>
+        <v>2.480318361048782</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>1.997732826962944e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.797880408501921</v>
+        <v>2.480311784713266</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>1.162890291091525e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.797880721933198</v>
+        <v>2.480314054662188</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.280563881834207e-07</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.797874578137222</v>
+        <v>2.480307568435511</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.797868893603194</v>
+        <v>2.480301609837373</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.79786414232798</v>
+        <v>2.480296940568736</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.797858853180418</v>
+        <v>2.480291651421174</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.797858830446117</v>
+        <v>2.480291628686873</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.797859148726333</v>
+        <v>2.480291946967089</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.797860239972791</v>
+        <v>2.480293038213546</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.797859550365655</v>
+        <v>2.48029234860641</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.797859580678056</v>
+        <v>2.480292378918812</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.797859391225546</v>
+        <v>2.480292189466302</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.797859444272249</v>
+        <v>2.480292242513005</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.797859497318952</v>
+        <v>2.480292295559708</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.79785945942845</v>
+        <v>2.480292257669205</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.797859330600743</v>
+        <v>2.480292128841499</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.797859186616836</v>
+        <v>2.480291984857591</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.79785908052343</v>
+        <v>2.480291878764186</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.797858845602318</v>
+        <v>2.480291643843073</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.797859012320526</v>
+        <v>2.480291810561282</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.797859209351137</v>
+        <v>2.480292007591892</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.797859050211029</v>
+        <v>2.480291848451784</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.79785908810153</v>
+        <v>2.480291886342286</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.797859285132141</v>
+        <v>2.480292083372897</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.79785926239784</v>
+        <v>2.480292060638595</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.797859133570133</v>
+        <v>2.480291931810888</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.797859141148233</v>
+        <v>2.480291939388989</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.797859406381747</v>
+        <v>2.480292204622503</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.797859353335044</v>
+        <v>2.4802921515758</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.797859436694148</v>
+        <v>2.480292234934904</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.79785926997594</v>
+        <v>2.480292068216695</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.79785945942845</v>
+        <v>2.480292257669205</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.797858906227121</v>
+        <v>2.480291704467877</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.797859019898627</v>
+        <v>2.480291818139383</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.797858800133715</v>
+        <v>2.480291598374471</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.797858860758518</v>
+        <v>2.480291658999274</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.797858731930812</v>
+        <v>2.480291530171568</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.797858868336619</v>
+        <v>2.480291666577374</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.797859042632928</v>
+        <v>2.480291840873684</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.797859186616836</v>
+        <v>2.480291984857591</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.797859019898627</v>
+        <v>2.480291818139383</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.797859012320526</v>
+        <v>2.480291810561282</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.797858724352711</v>
+        <v>2.480291522593467</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.797858739508913</v>
+        <v>2.480291537749668</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.797858966851924</v>
+        <v>2.48029176509268</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.797858951695724</v>
+        <v>2.480291749936479</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.797859057789129</v>
+        <v>2.480291856029885</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.797858784977515</v>
+        <v>2.48029158321827</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.79785888349282</v>
+        <v>2.480291681733576</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.797859050211029</v>
+        <v>2.480291848451784</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.797859209351137</v>
+        <v>2.480292007591892</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.797859042632928</v>
+        <v>2.480291840873684</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.797858997164326</v>
+        <v>2.480291795405082</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.797858982008125</v>
+        <v>2.48029178024888</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.797859019898627</v>
+        <v>2.480291818139383</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_1_000007.xlsx
+++ b/out/Attention_Base_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0003604460507631302</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.338792640423968</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0002934262156486511</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.839195093615979</v>
+        <v>0.04999999999999988</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.001310608349740505</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.039195093615978</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.006386767141520977</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.038390187231957</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.007998673245310783</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.0375852808479359</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.007470920216292143</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.0375852808479359</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.006007315590977669</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.005616101901978254</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.004624772816896439</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.00415390357375145</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.003645026125013828</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.002924394328147173</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.002563696354627609</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.002480851486325264</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002687666565179825</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.002453075721859932</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.002170921303331852</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001855616457760334</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001802518963813782</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001571785658597946</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001597013790160418</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.00209117354825139</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.002392514143139124</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.002369866240769625</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.002250766381621361</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.002131215762346983</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.001916920300573111</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.001854522153735161</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.001867154613137245</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001805481035262346</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001661111600697041</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001606188714504242</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.00145032862201333</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.001348360907286406</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001592195592820644</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.002762180287390947</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003924479708075523</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.004655694123357534</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.76145628024824e-05</v>
+        <v>-3.441802114946768e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.010066510700142</v>
+        <v>0.3967888760374763</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.005461786407977343</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.02169440194039</v>
+        <v>0.7941912676247608</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1514639789595488</v>
+        <v>0.0595002846383187</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.005972809158265591</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.313200200967344</v>
+        <v>0.5158702640959101</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1893792001503588</v>
+        <v>0.07439471593848709</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.006364278960973024</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.540518789421072</v>
+        <v>0.6051688603947142</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2714741853033066</v>
+        <v>0.1066444724881971</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.007031942252069712</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.89419504712886</v>
+        <v>0.744105073663596</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2904239527861504</v>
+        <v>0.114088461448183</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.008199665695428848</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.203588682699544</v>
+        <v>0.8656454752919374</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3077908522944665</v>
+        <v>0.1209107735406293</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.01011333614587784</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.528768410879833</v>
+        <v>0.9933871939977117</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1389002871077845</v>
+        <v>0.05456478330665339</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01188310142606497</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.498522359825531</v>
+        <v>0.981505510697955</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06708184685886588</v>
+        <v>0.02635165320710885</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01520599331706762</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.493678136931575</v>
+        <v>0.9796025348604981</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0319625028745364</v>
+        <v>0.01255459099981437</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01501220185309649</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.490467962910455</v>
+        <v>0.9783402633769335</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009468526714113601</v>
+        <v>0.003716690737052452</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01634348928928375</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.477409343390351</v>
+        <v>0.9732071272224644</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006261376347014713</v>
+        <v>0.002456756377466587</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01718030869960785</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.480459613366261</v>
+        <v>0.974402395117587</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003201709727720796</v>
+        <v>0.001254462550316852</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01787018403410912</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.480598914208837</v>
+        <v>0.9744540843074243</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001635859284060201</v>
+        <v>0.0006392637679745575</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01763984188437462</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.480666030930016</v>
+        <v>0.9744774228095501</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006118612075041338</v>
+        <v>0.0002372031734985556</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01760014146566391</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.480252650935008</v>
+        <v>0.9743118272127244</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003307774327442512</v>
+        <v>0.0001270009563613764</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01809823885560036</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.480302826466306</v>
+        <v>0.9743285592302303</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000157124909913899</v>
+        <v>5.857839604466628e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01824361085891724</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.480285261005901</v>
+        <v>0.9743186012862977</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.536342197837412e-05</v>
+        <v>3.435820469740162e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01848130114376545</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.480318787128652</v>
+        <v>0.9743288990222393</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.749782703175804e-05</v>
+        <v>1.558738314970903e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01902490481734276</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.480318361048782</v>
+        <v>0.9743257381850103</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.997732826962944e-05</v>
+        <v>4.990931307851776e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01701463013887405</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.480311784713266</v>
+        <v>0.9743200894633627</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.162890291091525e-05</v>
+        <v>1.395731888813558e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01983384788036346</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.480314054662188</v>
+        <v>0.9743181659872784</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>-1.503166167089948e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.02149450033903122</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.480307568435511</v>
+        <v>0.974312479709693</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0215870626270771</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.480301609837373</v>
+        <v>0.9743070692397754</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02135623618960381</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.480296940568736</v>
+        <v>0.974302234605457</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0210218820720911</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.480291651421174</v>
+        <v>0.9743020906215494</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.02104029804468155</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.480291628686873</v>
+        <v>0.974302067887248</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02089053951203823</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.480291946967089</v>
+        <v>0.9743023861674648</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01986568793654442</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.480293038213546</v>
+        <v>0.9743034774139216</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.02422106079757214</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.48029234860641</v>
+        <v>0.9743027878067857</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02993572875857353</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.480292378918812</v>
+        <v>0.9743028181191874</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.03292021900415421</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.480292189466302</v>
+        <v>0.9743026286666773</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.03441797941923141</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.480292242513005</v>
+        <v>0.9743026817133802</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.03700420260429382</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.480292295559708</v>
+        <v>0.974302734760083</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.03720755875110626</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.480292257669205</v>
+        <v>0.974302696869581</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.03508369624614716</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.480292128841499</v>
+        <v>0.9743025680418743</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.03357290476560593</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.480291984857591</v>
+        <v>0.9743024240579667</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.03299010545015335</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.480291825717483</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.03306356817483902</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.480291878764186</v>
+        <v>0.9743023179645612</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.03382043540477753</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.480291825717483</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.03233093023300171</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.480291825717483</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.03068643249571323</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.480291643843073</v>
+        <v>0.9743020830434489</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.03141003847122192</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.480291810561282</v>
+        <v>0.9743022497616576</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.03256190568208694</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.480292007591892</v>
+        <v>0.974302446792268</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.03320623934268951</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.480291848451784</v>
+        <v>0.9743022876521595</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.03179441392421722</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.480291886342286</v>
+        <v>0.9743023255426616</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.03083772584795952</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.480292083372897</v>
+        <v>0.9743025225732718</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.03228200972080231</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.480292060638595</v>
+        <v>0.9743024998389705</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.03272739425301552</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.480291909076587</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.03222473710775375</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.480291833295583</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.03202829882502556</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.480291931810888</v>
+        <v>0.9743023710112639</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.0304562970995903</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.480291939388989</v>
+        <v>0.9743023785893642</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03153738006949425</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.480292204622503</v>
+        <v>0.9743026438228781</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.03196987137198448</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.480291909076587</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.03160363435745239</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.4802921515758</v>
+        <v>0.9743025907761755</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.03290534019470215</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.480292234934904</v>
+        <v>0.9743026741352798</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02860765904188156</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.480292068216695</v>
+        <v>0.9743025074170711</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.03092601150274277</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.480292257669205</v>
+        <v>0.974302696869581</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.03066160529851913</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.480291909076587</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.03133662417531013</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.480291704467877</v>
+        <v>0.9743021436682521</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.03164682537317276</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.480291818139383</v>
+        <v>0.9743022573397581</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.03017136454582214</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.480291833295583</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0293206013739109</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.480291598374471</v>
+        <v>0.9743020375748466</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02993842586874962</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.480291658999274</v>
+        <v>0.9743020981996497</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.02981466241180897</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.480291530171568</v>
+        <v>0.974301969371943</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.0282116960734129</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.480291666577374</v>
+        <v>0.97430210577775</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.03066221252083778</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.480291840873684</v>
+        <v>0.9743022800740593</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.03105606883764267</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.480291984857591</v>
+        <v>0.9743024240579667</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0299974512308836</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.480291818139383</v>
+        <v>0.9743022573397581</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02884011156857014</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.480291810561282</v>
+        <v>0.9743022497616576</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02848485112190247</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.480291522593467</v>
+        <v>0.9743019617938425</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.02896461263298988</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.480291537749668</v>
+        <v>0.9743019769500434</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.02949690073728561</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.48029176509268</v>
+        <v>0.9743022042930553</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.02902947179973125</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.480291749936479</v>
+        <v>0.9743021891368544</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02960619889199734</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.480291856029885</v>
+        <v>0.9743022952302599</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.02841642871499062</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.48029158321827</v>
+        <v>0.9743020224186457</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02866669930517673</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.480291681733576</v>
+        <v>0.9743021209339509</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.02905596420168877</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.480291833295583</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.02904331684112549</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.480291848451784</v>
+        <v>0.9743022876521595</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.02866008877754211</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.480291825717483</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02839764766395092</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.480291909076587</v>
+        <v>0.9743023482769627</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02934719808399677</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.480292007591892</v>
+        <v>0.974302446792268</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02849662117660046</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.480291840873684</v>
+        <v>0.9743022800740593</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02803449705243111</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.480291825717483</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.02734903804957867</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.480291795405082</v>
+        <v>0.974302234605457</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.02723020873963833</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.48029178024888</v>
+        <v>0.9743022194492561</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.02734602615237236</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.480291818139383</v>
+        <v>0.9743022573397581</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.02688449248671532</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.480291833295583</v>
+        <v>0.9743022724959587</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.02588415704667568</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.480291825717483</v>
+        <v>0.9743022649178584</v>
       </c>
     </row>
   </sheetData>
